--- a/cancer_guidelines.xlsx
+++ b/cancer_guidelines.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>60mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>60mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>60mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -7427,7 +7427,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -7683,7 +7683,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>60mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -12365,7 +12365,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -16038,7 +16038,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -16164,7 +16164,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -17046,7 +17046,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -17235,7 +17235,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -17432,7 +17432,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -17499,7 +17499,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -17633,7 +17633,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -17767,7 +17767,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -17901,7 +17901,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -18035,7 +18035,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -18102,7 +18102,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -18169,7 +18169,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>2mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -18366,7 +18366,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -18433,7 +18433,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -18500,7 +18500,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -18701,7 +18701,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -18835,7 +18835,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -19237,7 +19237,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -19438,7 +19438,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -19639,7 +19639,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -19840,7 +19840,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -19907,7 +19907,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -19974,7 +19974,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -20041,7 +20041,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -20175,7 +20175,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>2mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -20242,7 +20242,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -20309,7 +20309,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -20644,7 +20644,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>2mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -20975,7 +20975,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -21042,7 +21042,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -21239,7 +21239,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -21432,7 +21432,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -21499,7 +21499,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -21692,7 +21692,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -21889,7 +21889,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -22023,7 +22023,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -22090,7 +22090,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -22157,7 +22157,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -22224,7 +22224,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -22354,7 +22354,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -22421,7 +22421,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -22614,7 +22614,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -22681,7 +22681,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -22874,7 +22874,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -22941,7 +22941,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -23071,7 +23071,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -23138,7 +23138,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -23272,7 +23272,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -23339,7 +23339,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -23406,7 +23406,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -23536,7 +23536,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -23863,7 +23863,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -23930,7 +23930,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -24060,7 +24060,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -24127,7 +24127,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -24257,7 +24257,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -24324,7 +24324,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -24521,7 +24521,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -24588,7 +24588,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -24655,7 +24655,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -24911,7 +24911,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -24978,7 +24978,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -25108,7 +25108,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -25175,7 +25175,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -25242,7 +25242,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -25309,7 +25309,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -25376,7 +25376,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -25443,7 +25443,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -25510,7 +25510,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -25644,7 +25644,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -25778,7 +25778,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -25904,7 +25904,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -26030,7 +26030,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -26219,7 +26219,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -26349,7 +26349,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -26416,7 +26416,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -26550,7 +26550,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -26818,7 +26818,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -26952,7 +26952,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -27082,7 +27082,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -27149,7 +27149,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -27216,7 +27216,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -27346,7 +27346,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -27413,7 +27413,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -27811,7 +27811,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -27941,7 +27941,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -28008,7 +28008,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -28142,7 +28142,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -28272,7 +28272,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -28339,7 +28339,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -28603,7 +28603,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -28670,7 +28670,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -28737,7 +28737,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -28871,7 +28871,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -29068,7 +29068,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -29135,7 +29135,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -29202,7 +29202,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -29269,7 +29269,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -29336,7 +29336,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>6mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -29470,7 +29470,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -29600,7 +29600,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -29734,7 +29734,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -29927,7 +29927,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -30187,7 +30187,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>50mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -30384,7 +30384,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -30451,7 +30451,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -30585,7 +30585,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -30719,7 +30719,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -30987,7 +30987,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -31054,7 +31054,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑，不需加水泡製)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -31589,7 +31589,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>2mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -31778,7 +31778,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -31845,7 +31845,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -31908,7 +31908,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -32101,7 +32101,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -32231,7 +32231,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -32298,7 +32298,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -32361,7 +32361,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -32617,7 +32617,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -32747,7 +32747,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -32810,7 +32810,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -32873,7 +32873,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -33664,7 +33664,7 @@
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t>25mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -33723,7 +33723,7 @@
       </c>
       <c r="M515" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -33900,7 +33900,7 @@
       </c>
       <c r="M518" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -34014,7 +34014,7 @@
       </c>
       <c r="M520" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -34191,7 +34191,7 @@
       </c>
       <c r="M523" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -34364,7 +34364,7 @@
       </c>
       <c r="M526" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -34596,7 +34596,7 @@
       </c>
       <c r="M530" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -34655,7 +34655,7 @@
       </c>
       <c r="M531" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -34773,7 +34773,7 @@
       </c>
       <c r="M533" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -34946,7 +34946,7 @@
       </c>
       <c r="M536" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="M538" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -35166,7 +35166,7 @@
       </c>
       <c r="M540" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -35280,7 +35280,7 @@
       <c r="L542" t="inlineStr"/>
       <c r="M542" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -35339,7 +35339,7 @@
       </c>
       <c r="M543" t="inlineStr">
         <is>
-          <t>20mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -35453,7 +35453,7 @@
       </c>
       <c r="M545" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -35512,7 +35512,7 @@
       </c>
       <c r="M546" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -35685,7 +35685,7 @@
       </c>
       <c r="M549" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -35803,7 +35803,7 @@
       </c>
       <c r="M551" t="inlineStr">
         <is>
-          <t>5mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="M552" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -36039,7 +36039,7 @@
       </c>
       <c r="M555" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -36153,7 +36153,7 @@
       </c>
       <c r="M557" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -36212,7 +36212,7 @@
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -36330,7 +36330,7 @@
       </c>
       <c r="M560" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -36507,7 +36507,7 @@
       </c>
       <c r="M563" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -36621,7 +36621,7 @@
       </c>
       <c r="M565" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="M567" t="inlineStr">
         <is>
-          <t>1mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
@@ -36853,7 +36853,7 @@
       </c>
       <c r="M569" t="inlineStr">
         <is>
-          <t>10mg/ml (液劑)</t>
+          <t>無</t>
         </is>
       </c>
     </row>
